--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="52">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="8" type="noConversion"/>
@@ -49,29 +49,10 @@
     <t>Desc</t>
   </si>
   <si>
-    <t>Radius</t>
-  </si>
-  <si>
     <t>!string</t>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>float</t>
-    </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -258,22 +239,7 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Skin</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>Path</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AOC_Enemy_01</t>
-  </si>
-  <si>
-    <t>AOC_Enemy_01</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -832,22 +798,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -858,7 +824,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="10"/>
@@ -867,30 +833,28 @@
     <col min="4" max="4" width="15.25" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.625" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.625" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>3</v>
@@ -899,721 +863,580 @@
         <v>4</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>5</v>
+        <v>51</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>8</v>
+        <v>47</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
       </c>
       <c r="I3" t="s">
         <v>16</v>
       </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="6">
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="6">
-        <v>30</v>
-      </c>
-      <c r="I4">
+        <v>48</v>
+      </c>
+      <c r="G4">
         <v>1001</v>
       </c>
-      <c r="J4">
+      <c r="H4">
         <v>10001</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="6">
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="6">
-        <v>30</v>
-      </c>
-      <c r="I5">
+        <v>48</v>
+      </c>
+      <c r="G5">
         <v>1001</v>
       </c>
-      <c r="J5">
+      <c r="H5">
         <v>10001</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6" s="6">
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H6" s="6">
-        <v>30</v>
-      </c>
-      <c r="I6">
+        <v>48</v>
+      </c>
+      <c r="G6">
         <v>1001</v>
       </c>
-      <c r="J6">
+      <c r="H6">
         <v>10001</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="6">
         <v>104</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H7" s="6">
-        <v>30</v>
-      </c>
-      <c r="I7">
+        <v>48</v>
+      </c>
+      <c r="G7">
         <v>1001</v>
       </c>
-      <c r="J7">
+      <c r="H7">
         <v>10001</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="6">
         <v>105</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="6">
-        <v>30</v>
-      </c>
-      <c r="I8">
+        <v>48</v>
+      </c>
+      <c r="G8">
         <v>1001</v>
       </c>
-      <c r="J8">
+      <c r="H8">
         <v>10001</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
       <c r="B9" s="6">
         <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="6">
-        <v>30</v>
-      </c>
-      <c r="I9">
+        <v>48</v>
+      </c>
+      <c r="G9">
         <v>1002</v>
       </c>
-      <c r="J9">
+      <c r="H9">
         <v>10002</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="6">
         <v>107</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="6">
-        <v>30</v>
-      </c>
-      <c r="I10">
+        <v>48</v>
+      </c>
+      <c r="G10">
         <v>1002</v>
       </c>
-      <c r="J10">
+      <c r="H10">
         <v>10002</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="6">
         <v>108</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H11" s="6">
-        <v>30</v>
-      </c>
-      <c r="I11">
+        <v>48</v>
+      </c>
+      <c r="G11">
         <v>1002</v>
       </c>
-      <c r="J11">
+      <c r="H11">
         <v>10002</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
       <c r="B12" s="6">
         <v>109</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="6">
-        <v>30</v>
-      </c>
-      <c r="I12">
+        <v>48</v>
+      </c>
+      <c r="G12">
         <v>1002</v>
       </c>
-      <c r="J12">
+      <c r="H12">
         <v>10002</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
       <c r="B13" s="6">
         <v>110</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H13" s="6">
-        <v>30</v>
-      </c>
-      <c r="I13">
+        <v>48</v>
+      </c>
+      <c r="G13">
         <v>1002</v>
       </c>
-      <c r="J13">
+      <c r="H13">
         <v>10002</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="B14" s="6">
         <v>111</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H14" s="6">
-        <v>30</v>
-      </c>
-      <c r="I14">
+        <v>48</v>
+      </c>
+      <c r="G14">
         <v>1003</v>
       </c>
-      <c r="J14">
+      <c r="H14">
         <v>10003</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
       <c r="B15" s="6">
         <v>112</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H15" s="6">
-        <v>30</v>
-      </c>
-      <c r="I15">
+        <v>48</v>
+      </c>
+      <c r="G15">
         <v>1003</v>
       </c>
-      <c r="J15">
+      <c r="H15">
         <v>10003</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
       <c r="B16" s="6">
         <v>113</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H16" s="6">
-        <v>30</v>
-      </c>
-      <c r="I16">
+        <v>48</v>
+      </c>
+      <c r="G16">
         <v>1003</v>
       </c>
-      <c r="J16">
+      <c r="H16">
         <v>10003</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="B17" s="6">
         <v>114</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H17" s="6">
-        <v>30</v>
-      </c>
-      <c r="I17">
+        <v>48</v>
+      </c>
+      <c r="G17">
         <v>1003</v>
       </c>
-      <c r="J17">
+      <c r="H17">
         <v>10003</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="6">
         <v>115</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H18" s="6">
-        <v>30</v>
-      </c>
-      <c r="I18">
+        <v>48</v>
+      </c>
+      <c r="G18">
         <v>1003</v>
       </c>
-      <c r="J18">
+      <c r="H18">
         <v>10003</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
       <c r="B19">
         <v>10001</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H19" s="2">
-        <v>40</v>
-      </c>
-      <c r="I19">
+        <v>49</v>
+      </c>
+      <c r="G19">
         <v>10001</v>
       </c>
-      <c r="J19">
+      <c r="H19">
         <v>10004</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20">
         <v>10002</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="E20" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H20" s="2">
-        <v>40</v>
-      </c>
-      <c r="I20">
+        <v>49</v>
+      </c>
+      <c r="G20">
         <v>10002</v>
       </c>
-      <c r="J20">
+      <c r="H20">
         <v>10004</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21">
         <v>10003</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H21" s="2">
-        <v>40</v>
-      </c>
-      <c r="I21">
+        <v>49</v>
+      </c>
+      <c r="G21">
         <v>10003</v>
       </c>
-      <c r="J21">
+      <c r="H21">
         <v>10004</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B22" s="6">
         <v>1000001</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H22" s="6">
         <v>50</v>
       </c>
-      <c r="I22">
+      <c r="G22">
         <v>1000001</v>
       </c>
-      <c r="J22">
+      <c r="H22">
         <v>10005</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B23" s="6">
         <v>1000002</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H23" s="6">
         <v>50</v>
       </c>
-      <c r="I23">
+      <c r="G23">
         <v>1000002</v>
       </c>
-      <c r="J23">
+      <c r="H23">
         <v>10005</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="B24" s="6">
         <v>1000003</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H24" s="6">
         <v>50</v>
       </c>
-      <c r="I24">
+      <c r="G24">
         <v>1000003</v>
       </c>
-      <c r="J24">
+      <c r="H24">
         <v>10005</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="21" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" ht="21" x14ac:dyDescent="0.45">
       <c r="C25" s="14"/>
       <c r="D25" s="7"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" spans="1:10" ht="21" x14ac:dyDescent="0.45">
+    </row>
+    <row r="26" spans="1:8" ht="21" x14ac:dyDescent="0.45">
       <c r="C26" s="14"/>
     </row>
-    <row r="27" spans="1:10" ht="21" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" ht="21" x14ac:dyDescent="0.45">
       <c r="C27" s="14"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
       <c r="E28" s="15"/>
       <c r="F28" s="15"/>
-      <c r="G28"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C30" s="16"/>
       <c r="D30"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C31" s="16"/>
       <c r="D31"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C32" s="16"/>
       <c r="D32"/>
     </row>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -774,7 +774,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="8" type="noConversion"/>
@@ -65,9 +65,6 @@
   </si>
   <si>
     <t>Normal</t>
-  </si>
-  <si>
-    <t>Normal</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -95,18 +92,10 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>BaseStatID</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>SkillSetID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>악마1</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -118,92 +107,6 @@
   </si>
   <si>
     <t>Elite</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Elite</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골전사1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골전사2</t>
-  </si>
-  <si>
-    <t>해골전사3</t>
-  </si>
-  <si>
-    <t>버섯1-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>버섯1-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>버섯1-3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린1-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린1-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>버섯3-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>버섯3-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>버섯3-3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린3-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린3-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>버섯2-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>버섯2-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>버섯2-3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린2-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린2-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>버섯</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골전사</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -227,10 +130,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Prefab_Monster_01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>Prefab_Monster_02</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -240,6 +139,42 @@
   </si>
   <si>
     <t>Path</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골전사1-1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골궁수1-1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골마법사1-1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골 궁수</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골 전사</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골 마법사</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseSkillSet</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -449,7 +384,7 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -497,6 +432,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -774,7 +715,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -803,17 +744,17 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -824,7 +765,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="10"/>
@@ -834,7 +775,7 @@
     <col min="5" max="5" width="14.625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.375" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.625" customWidth="1"/>
     <col min="16" max="16384" width="9" style="2"/>
@@ -854,7 +795,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>3</v>
@@ -863,16 +804,16 @@
         <v>4</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>33</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -881,7 +822,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>5</v>
@@ -890,555 +831,184 @@
         <v>5</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
-      <c r="B4" s="6">
-        <v>101</v>
+      <c r="B4">
+        <v>10001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>1001</v>
-      </c>
-      <c r="H4">
+        <v>10001</v>
+      </c>
+      <c r="H4" s="20">
         <v>10001</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
-      <c r="B5" s="6">
-        <v>102</v>
+      <c r="B5">
+        <v>10002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>1001</v>
-      </c>
-      <c r="H5">
-        <v>10001</v>
+        <v>10002</v>
+      </c>
+      <c r="H5" s="20">
+        <v>10002</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
-      <c r="B6" s="6">
-        <v>103</v>
+      <c r="B6">
+        <v>10003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>1001</v>
-      </c>
-      <c r="H6">
-        <v>10001</v>
+        <v>10003</v>
+      </c>
+      <c r="H6" s="20">
+        <v>10003</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
       <c r="B7" s="6">
-        <v>104</v>
+        <v>1000001</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>31</v>
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>1001</v>
-      </c>
-      <c r="H7">
-        <v>10001</v>
+        <v>1000001</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
       <c r="B8" s="6">
-        <v>105</v>
+        <v>1000002</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>32</v>
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>1001</v>
-      </c>
-      <c r="H8">
-        <v>10001</v>
+        <v>1000002</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
       <c r="B9" s="6">
-        <v>106</v>
+        <v>1000003</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G9">
-        <v>1002</v>
-      </c>
-      <c r="H9">
-        <v>10002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="6">
-        <v>107</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10">
-        <v>1002</v>
-      </c>
-      <c r="H10">
-        <v>10002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="6">
-        <v>108</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11">
-        <v>1002</v>
-      </c>
-      <c r="H11">
-        <v>10002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="6">
-        <v>109</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G12">
-        <v>1002</v>
-      </c>
-      <c r="H12">
-        <v>10002</v>
-      </c>
+        <v>1000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="21" x14ac:dyDescent="0.45">
+      <c r="C10" s="14"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" ht="21" x14ac:dyDescent="0.45">
+      <c r="C11" s="14"/>
+    </row>
+    <row r="12" spans="1:9" ht="21" x14ac:dyDescent="0.45">
+      <c r="C12" s="14"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="6">
-        <v>110</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13">
-        <v>1002</v>
-      </c>
-      <c r="H13">
-        <v>10002</v>
-      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="15"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="6">
-        <v>111</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14">
-        <v>1003</v>
-      </c>
-      <c r="H14">
-        <v>10003</v>
-      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="6">
-        <v>112</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15">
-        <v>1003</v>
-      </c>
-      <c r="H15">
-        <v>10003</v>
-      </c>
+      <c r="C15" s="16"/>
+      <c r="D15"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="6">
-        <v>113</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G16">
-        <v>1003</v>
-      </c>
-      <c r="H16">
-        <v>10003</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="6">
-        <v>114</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17">
-        <v>1003</v>
-      </c>
-      <c r="H17">
-        <v>10003</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="6">
-        <v>115</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G18">
-        <v>1003</v>
-      </c>
-      <c r="H18">
-        <v>10003</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
-      <c r="B19">
-        <v>10001</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19">
-        <v>10001</v>
-      </c>
-      <c r="H19">
-        <v>10004</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20">
-        <v>10002</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G20">
-        <v>10002</v>
-      </c>
-      <c r="H20">
-        <v>10004</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
-      <c r="B21">
-        <v>10003</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G21">
-        <v>10003</v>
-      </c>
-      <c r="H21">
-        <v>10004</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="6">
-        <v>1000001</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G22">
-        <v>1000001</v>
-      </c>
-      <c r="H22">
-        <v>10005</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="6">
-        <v>1000002</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G23">
-        <v>1000002</v>
-      </c>
-      <c r="H23">
-        <v>10005</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="6">
-        <v>1000003</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G24">
-        <v>1000003</v>
-      </c>
-      <c r="H24">
-        <v>10005</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="21" x14ac:dyDescent="0.45">
-      <c r="C25" s="14"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-    </row>
-    <row r="26" spans="1:8" ht="21" x14ac:dyDescent="0.45">
-      <c r="C26" s="14"/>
-    </row>
-    <row r="27" spans="1:8" ht="21" x14ac:dyDescent="0.45">
-      <c r="C27" s="14"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C30" s="16"/>
-      <c r="D30"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C31" s="16"/>
-      <c r="D31"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C32" s="16"/>
-      <c r="D32"/>
+      <c r="C16" s="16"/>
+      <c r="D16"/>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C17" s="16"/>
+      <c r="D17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -31,10 +31,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
@@ -53,61 +53,57 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Monster</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MonsterTypes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Boss</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MonsterType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!MonsterTypes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DropID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>BaseStatID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>악마1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>악마2</t>
   </si>
   <si>
     <t>악마3</t>
-  </si>
-  <si>
-    <t>Elite</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>악마</t>
@@ -127,67 +123,91 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_Monster_02</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_Monster_03</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Path</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>해골전사1-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>해골궁수1-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>해골마법사1-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>해골 궁수</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>해골 전사</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>해골 마법사</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>BaseSkillSet</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elite</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elite</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골장군1-1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골 장군</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -376,13 +396,13 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -398,46 +418,46 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -715,7 +735,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -749,7 +769,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -758,14 +778,14 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="10"/>
@@ -804,13 +824,13 @@
         <v>4</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
         <v>16</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I2" t="s">
         <v>14</v>
@@ -831,13 +851,13 @@
         <v>5</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I3" t="s">
         <v>15</v>
@@ -849,16 +869,16 @@
         <v>10001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4">
         <v>10001</v>
@@ -873,16 +893,16 @@
         <v>10002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5">
         <v>10002</v>
@@ -897,16 +917,16 @@
         <v>10003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6">
         <v>10003</v>
@@ -916,91 +936,111 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="6">
-        <v>1000001</v>
+      <c r="A7" s="9"/>
+      <c r="B7">
+        <v>20001</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G7">
-        <v>1000001</v>
+        <v>20001</v>
+      </c>
+      <c r="H7" s="20">
+        <v>10001</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="6">
-        <v>1000002</v>
+        <v>1000001</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G8">
+        <v>1000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="6">
         <v>1000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="6">
-        <v>1000003</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9">
+        <v>1000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="6">
+        <v>1000003</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9">
+      <c r="E10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10">
         <v>1000003</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="21" x14ac:dyDescent="0.45">
-      <c r="C10" s="14"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:9" ht="21" x14ac:dyDescent="0.45">
       <c r="C11" s="14"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="21" x14ac:dyDescent="0.45">
       <c r="C12" s="14"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="15"/>
+    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.45">
+      <c r="C13" s="14"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
+      <c r="E14" s="15"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="16"/>
-      <c r="D15"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C16" s="16"/>
@@ -1010,8 +1050,12 @@
       <c r="C17" s="16"/>
       <c r="D17"/>
     </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C18" s="16"/>
+      <c r="D18"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="9" type="noConversion"/>
@@ -187,6 +187,10 @@
   </si>
   <si>
     <t>해골 장군</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab_Monster_01</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -735,7 +739,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -878,7 +882,7 @@
         <v>29</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G4">
         <v>10001</v>
@@ -902,7 +906,7 @@
         <v>28</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G5">
         <v>10002</v>
@@ -926,7 +930,7 @@
         <v>30</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G6">
         <v>10003</v>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -31,10 +31,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
@@ -53,57 +53,51 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Monster</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>MonsterTypes</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Boss</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>MonsterType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!MonsterTypes</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>DropID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>BaseStatID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>악마1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>악마2</t>
-  </si>
-  <si>
-    <t>악마3</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>악마</t>
@@ -123,87 +117,94 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_Monster_02</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefab_Monster_03</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Path</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>해골전사1-1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>해골궁수1-1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>해골마법사1-1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>해골 궁수</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>해골 전사</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>해골 마법사</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>BaseSkillSet</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Elite</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Elite</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>해골장군1-1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>해골 장군</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_Monster_01</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab_BossMonster_01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -400,15 +401,15 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -422,46 +423,49 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -773,7 +777,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -782,7 +786,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -797,7 +801,7 @@
     <col min="3" max="3" width="14.125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.25" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.625" bestFit="1" customWidth="1"/>
@@ -828,13 +832,13 @@
         <v>4</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
         <v>16</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s">
         <v>14</v>
@@ -855,13 +859,13 @@
         <v>5</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I3" t="s">
         <v>15</v>
@@ -873,16 +877,16 @@
         <v>10001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G4">
         <v>10001</v>
@@ -897,16 +901,16 @@
         <v>10002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G5">
         <v>10002</v>
@@ -921,16 +925,16 @@
         <v>10003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G6">
         <v>10003</v>
@@ -945,16 +949,16 @@
         <v>20001</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G7">
         <v>20001</v>
@@ -965,7 +969,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="6">
-        <v>1000001</v>
+        <v>30001</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
@@ -974,61 +978,30 @@
         <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G8">
-        <v>1000001</v>
+        <v>30001</v>
+      </c>
+      <c r="H8">
+        <v>10004</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="6">
-        <v>1000002</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9">
-        <v>1000002</v>
-      </c>
+      <c r="B9" s="6"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
-      <c r="B10" s="6">
-        <v>1000003</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10">
-        <v>1000003</v>
-      </c>
+      <c r="B10" s="6"/>
     </row>
     <row r="11" spans="1:9" ht="21" x14ac:dyDescent="0.45">
+      <c r="B11" s="6"/>
       <c r="C11" s="14"/>
-      <c r="D11" s="7"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="21" x14ac:dyDescent="0.45">
       <c r="C12" s="14"/>
@@ -1059,7 +1032,7 @@
       <c r="D18"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
     <sheet name="#Monster" sheetId="7" r:id="rId2"/>
+    <sheet name="#MonsterPhase" sheetId="8" r:id="rId3"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="54">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="10" type="noConversion"/>
@@ -185,6 +186,100 @@
   </si>
   <si>
     <t>Prefab_BossMonster_01</t>
+  </si>
+  <si>
+    <t>MonsterPhase</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phase1_SkillSet</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phase1_Hp</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phase2_Hp</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phase2_SkillSet</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phase3_Hp</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phase3_SkillSet</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phase4_Hp</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phase4_SkillSet</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Phase</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Count</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>악마보스 페이즈별 스킬들</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phase1_to_2_TransitionSkill</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phase2_to_3_TransitionSkill</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phase3_to_4_TransitionSkill</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -409,7 +504,7 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -466,6 +561,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -743,7 +847,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -817,7 +921,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="6" t="s">
         <v>2</v>
@@ -844,7 +948,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="12" t="s">
         <v>6</v>
@@ -871,7 +975,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4">
         <v>10001</v>
@@ -894,8 +998,9 @@
       <c r="H4" s="20">
         <v>10001</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I4"/>
+    </row>
+    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5">
         <v>10002</v>
@@ -918,8 +1023,9 @@
       <c r="H5" s="20">
         <v>10002</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I5"/>
+    </row>
+    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6">
         <v>10003</v>
@@ -942,8 +1048,9 @@
       <c r="H6" s="20">
         <v>10003</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I6"/>
+    </row>
+    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7">
         <v>20001</v>
@@ -966,8 +1073,10 @@
       <c r="H7" s="20">
         <v>10001</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I7"/>
+    </row>
+    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10"/>
       <c r="B8" s="6">
         <v>30001</v>
       </c>
@@ -989,47 +1098,400 @@
       <c r="H8">
         <v>10004</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I8"/>
+    </row>
+    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="10"/>
       <c r="B9" s="6"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+    </row>
+    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="6"/>
-    </row>
-    <row r="11" spans="1:9" ht="21" x14ac:dyDescent="0.45">
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+    </row>
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.45">
+      <c r="A11" s="10"/>
       <c r="B11" s="6"/>
       <c r="C11" s="14"/>
       <c r="D11" s="21"/>
       <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" ht="21" x14ac:dyDescent="0.45">
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+    </row>
+    <row r="12" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.45">
+      <c r="A12" s="10"/>
       <c r="C12" s="14"/>
-    </row>
-    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.45">
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+    </row>
+    <row r="13" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.45">
+      <c r="A13" s="10"/>
       <c r="C13" s="14"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+    </row>
+    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
       <c r="E14" s="15"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+    </row>
+    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+    </row>
+    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="10"/>
       <c r="C16" s="16"/>
       <c r="D16"/>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+    </row>
+    <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="10"/>
       <c r="C17" s="16"/>
       <c r="D17"/>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10"/>
       <c r="C18" s="16"/>
       <c r="D18"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R16"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="10"/>
+    <col min="2" max="2" width="8.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="9"/>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="N2" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="9"/>
+      <c r="B3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N3" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="9"/>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2">
+        <v>100</v>
+      </c>
+      <c r="F4" s="2">
+        <v>10001</v>
+      </c>
+      <c r="H4" s="24">
+        <v>75</v>
+      </c>
+      <c r="I4" s="2">
+        <v>10002</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="20">
+        <v>50</v>
+      </c>
+      <c r="L4" s="2">
+        <v>10003</v>
+      </c>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2">
+        <v>25</v>
+      </c>
+      <c r="O4" s="2">
+        <v>10004</v>
+      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B8" s="6">
+        <v>5</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B9" s="6"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="6"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B11" s="6"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="5"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="15"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -35,7 +35,7 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="54">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
@@ -54,51 +54,51 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Monster</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>MonsterTypes</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Boss</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>MonsterType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!MonsterTypes</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>DropID</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>BaseStatID</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>악마1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>악마</t>
@@ -118,78 +118,78 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_Monster_02</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Path</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>해골전사1-1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>해골궁수1-1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>해골마법사1-1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>해골 궁수</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>해골 전사</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>해골 마법사</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>BaseSkillSet</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Elite</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Elite</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>해골장군1-1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>해골 장군</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_Monster_01</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_BossMonster_01</t>
   </si>
   <si>
     <t>MonsterPhase</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -206,43 +206,43 @@
       </rPr>
       <t>int</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Phase1_SkillSet</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Phase1_Hp</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Phase2_Hp</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Phase2_SkillSet</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Phase3_Hp</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Phase3_SkillSet</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Phase4_Hp</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Phase4_SkillSet</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -259,39 +259,47 @@
       </rPr>
       <t>Count</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>악마보스 페이즈별 스킬들</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Phase1_to_2_TransitionSkill</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!SkillInfo</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Phase2_to_3_TransitionSkill</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Phase3_to_4_TransitionSkill</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -496,13 +504,13 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -518,55 +526,55 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -847,7 +855,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -890,7 +898,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1175,7 +1183,7 @@
       <c r="D18"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1494,7 +1502,7 @@
       <c r="R16" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="54">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="11" type="noConversion"/>
@@ -121,10 +121,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>Prefab_Monster_02</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>Path</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -279,6 +275,10 @@
   </si>
   <si>
     <t>Phase3_to_4_TransitionSkill</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab_Monster_02</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -889,7 +889,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -905,7 +905,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="10"/>
@@ -921,7 +921,7 @@
     <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
@@ -929,7 +929,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="6" t="s">
         <v>2</v>
@@ -944,19 +944,25 @@
         <v>4</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
         <v>16</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="12" t="s">
         <v>6</v>
@@ -977,28 +983,34 @@
         <v>13</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
-      <c r="B4">
-        <v>10001</v>
+      <c r="B4" s="12">
+        <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G4">
         <v>10001</v>
@@ -1006,181 +1018,350 @@
       <c r="H4" s="20">
         <v>10001</v>
       </c>
-      <c r="I4"/>
-    </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
-      <c r="B5">
-        <v>10002</v>
+      <c r="B5" s="12">
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="H5" s="20">
-        <v>10002</v>
-      </c>
-      <c r="I5"/>
-    </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+        <v>10001</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
-      <c r="B6">
-        <v>10003</v>
+      <c r="B6" s="12">
+        <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="H6" s="20">
-        <v>10003</v>
-      </c>
-      <c r="I6"/>
-    </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+        <v>10001</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7">
-        <v>20001</v>
+        <v>10001</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="G7">
-        <v>20001</v>
+        <v>10001</v>
       </c>
       <c r="H7" s="20">
         <v>10001</v>
       </c>
-      <c r="I7"/>
-    </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10"/>
-      <c r="B8" s="6">
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8">
+        <v>10002</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8">
+        <v>10002</v>
+      </c>
+      <c r="H8" s="20">
+        <v>10002</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9">
+        <v>10003</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9">
+        <v>10003</v>
+      </c>
+      <c r="H9" s="20">
+        <v>10003</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10">
+        <v>20001</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10">
+        <v>20001</v>
+      </c>
+      <c r="H10" s="20">
+        <v>10001</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B11" s="6">
         <v>30001</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8">
+      <c r="F11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11">
         <v>30001</v>
       </c>
-      <c r="H8">
+      <c r="H11">
         <v>10004</v>
       </c>
-      <c r="I8"/>
-    </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10"/>
-      <c r="B9" s="6"/>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-    </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="6"/>
-      <c r="G10"/>
-      <c r="H10"/>
-      <c r="I10"/>
-    </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.45">
-      <c r="A11" s="10"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="5"/>
-      <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
-    </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.45">
-      <c r="A12" s="10"/>
-      <c r="C12" s="14"/>
-      <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
-    </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.45">
-      <c r="A13" s="10"/>
-      <c r="C13" s="14"/>
-      <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13"/>
-    </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="15"/>
-      <c r="G14"/>
-      <c r="H14"/>
-      <c r="I14"/>
-    </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="10"/>
-      <c r="C15" s="12"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B12" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12">
+        <v>30001</v>
+      </c>
+      <c r="H12">
+        <v>10004</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="6"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" spans="1:15" ht="21" x14ac:dyDescent="0.45">
+      <c r="B14" s="6"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="5"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+    </row>
+    <row r="15" spans="1:15" ht="21" x14ac:dyDescent="0.45">
+      <c r="C15" s="14"/>
       <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15"/>
-    </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="10"/>
-      <c r="C16" s="16"/>
-      <c r="D16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-    </row>
-    <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="10"/>
-      <c r="C17" s="16"/>
-      <c r="D17"/>
-    </row>
-    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="10"/>
-      <c r="C18" s="16"/>
-      <c r="D18"/>
+      <c r="E15" s="6"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+    </row>
+    <row r="16" spans="1:15" ht="21" x14ac:dyDescent="0.45">
+      <c r="C16" s="14"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="15"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C19" s="16"/>
+      <c r="D19"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C20" s="16"/>
+      <c r="D20"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C21" s="16"/>
+      <c r="D21"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -1217,7 +1398,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -1229,40 +1410,40 @@
         <v>3</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E2" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="23" t="s">
+      <c r="I2" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="J2" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="K2" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="L2" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="K2" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="L2" s="23" t="s">
+      <c r="N2" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M2" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="N2" s="23" t="s">
+      <c r="O2" s="23" t="s">
         <v>46</v>
-      </c>
-      <c r="O2" s="23" t="s">
-        <v>47</v>
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
@@ -1277,40 +1458,40 @@
         <v>5</v>
       </c>
       <c r="D3" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="G3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" s="23" t="s">
+      <c r="J3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K3" s="23" t="s">
+      <c r="M3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N3" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N3" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
@@ -1322,7 +1503,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4" s="2">
         <v>4</v>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -855,7 +855,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="55">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="11" type="noConversion"/>
@@ -279,6 +279,10 @@
   </si>
   <si>
     <t>Prefab_Monster_02</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>레이드보스 악마1</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -855,7 +859,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -905,13 +909,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="10"/>
     <col min="2" max="2" width="8.5" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.5" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
@@ -997,11 +1001,11 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
-      <c r="B4" s="12">
-        <v>101</v>
+      <c r="B4">
+        <v>10001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>21</v>
@@ -1027,26 +1031,26 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
-      <c r="B5" s="12">
-        <v>102</v>
+      <c r="B5">
+        <v>10002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G5">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="H5" s="20">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1057,26 +1061,26 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
-      <c r="B6" s="12">
-        <v>103</v>
+      <c r="B6">
+        <v>10003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G6">
-        <v>10001</v>
+        <v>10003</v>
       </c>
       <c r="H6" s="20">
-        <v>10001</v>
+        <v>10003</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -1088,25 +1092,25 @@
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7">
-        <v>10001</v>
+        <v>20001</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="G7">
-        <v>10001</v>
+        <v>20001</v>
       </c>
       <c r="H7" s="20">
-        <v>10001</v>
+        <v>20001</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -1116,27 +1120,26 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8">
-        <v>10002</v>
+      <c r="B8" s="6">
+        <v>30001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8">
-        <v>10002</v>
-      </c>
-      <c r="H8" s="20">
-        <v>10002</v>
+        <v>30001</v>
+      </c>
+      <c r="H8">
+        <v>30001</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -1146,27 +1149,26 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9">
-        <v>10003</v>
+      <c r="B9" s="6">
+        <v>100001</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G9">
-        <v>10003</v>
-      </c>
-      <c r="H9" s="20">
-        <v>10003</v>
+        <v>100001</v>
+      </c>
+      <c r="H9">
+        <v>100001</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -1177,27 +1179,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
-      <c r="B10">
-        <v>20001</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10">
-        <v>20001</v>
-      </c>
-      <c r="H10" s="20">
-        <v>10001</v>
-      </c>
+      <c r="B10" s="6"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -1205,28 +1187,11 @@
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B11" s="6">
-        <v>30001</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11">
-        <v>30001</v>
-      </c>
-      <c r="H11">
-        <v>10004</v>
-      </c>
+    <row r="11" spans="1:15" ht="21" x14ac:dyDescent="0.45">
+      <c r="B11" s="6"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="5"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -1234,28 +1199,10 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B12" s="6">
-        <v>1000001</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12">
-        <v>30001</v>
-      </c>
-      <c r="H12">
-        <v>10004</v>
-      </c>
+    <row r="12" spans="1:15" ht="21" x14ac:dyDescent="0.45">
+      <c r="C12" s="14"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="6"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -1263,9 +1210,8 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="6"/>
+    <row r="13" spans="1:15" ht="21" x14ac:dyDescent="0.45">
+      <c r="C13" s="14"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
@@ -1273,11 +1219,10 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="21" x14ac:dyDescent="0.45">
-      <c r="B14" s="6"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="5"/>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="15"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
@@ -1285,10 +1230,10 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="21" x14ac:dyDescent="0.45">
-      <c r="C15" s="14"/>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C15" s="12"/>
       <c r="D15" s="12"/>
-      <c r="E15" s="6"/>
+      <c r="E15" s="12"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
@@ -1296,8 +1241,9 @@
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="21" x14ac:dyDescent="0.45">
-      <c r="C16" s="14"/>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C16" s="16"/>
+      <c r="D16"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
@@ -1306,9 +1252,11 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="15"/>
+      <c r="C17" s="16"/>
+      <c r="D17"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -1317,51 +1265,17 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
+      <c r="C18" s="16"/>
+      <c r="D18"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C19" s="16"/>
-      <c r="D19"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C20" s="16"/>
-      <c r="D20"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C21" s="16"/>
-      <c r="D21"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="53">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="11" type="noConversion"/>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>MonsterTypes</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>Normal</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -78,14 +74,6 @@
   </si>
   <si>
     <t>!MonsterTypes</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>DropID</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -283,6 +271,10 @@
   </si>
   <si>
     <t>레이드보스 악마1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterTypes</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -859,7 +851,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -883,22 +875,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -909,7 +901,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="10"/>
@@ -920,12 +912,11 @@
     <col min="6" max="6" width="22.5" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.625" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="9" max="9" width="12.625" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
@@ -933,13 +924,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>3</v>
@@ -948,31 +939,28 @@
         <v>4</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="12" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>5</v>
@@ -981,40 +969,37 @@
         <v>5</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4">
         <v>10001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G4">
         <v>10001</v>
@@ -1022,29 +1007,29 @@
       <c r="H4" s="20">
         <v>10001</v>
       </c>
+      <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5">
         <v>10002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G5">
         <v>10002</v>
@@ -1052,29 +1037,29 @@
       <c r="H5" s="20">
         <v>10002</v>
       </c>
+      <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6">
         <v>10003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G6">
         <v>10003</v>
@@ -1082,29 +1067,29 @@
       <c r="H6" s="20">
         <v>10003</v>
       </c>
+      <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7">
         <v>20001</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G7">
         <v>20001</v>
@@ -1112,28 +1097,28 @@
       <c r="H7" s="20">
         <v>20001</v>
       </c>
+      <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B8" s="6">
         <v>30001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G8">
         <v>30001</v>
@@ -1141,28 +1126,28 @@
       <c r="H8">
         <v>30001</v>
       </c>
+      <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B9" s="6">
         <v>100001</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G9">
         <v>100001</v>
@@ -1170,88 +1155,88 @@
       <c r="H9">
         <v>100001</v>
       </c>
+      <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="6"/>
+      <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-    </row>
-    <row r="11" spans="1:15" ht="21" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:14" ht="21" x14ac:dyDescent="0.45">
       <c r="B11" s="6"/>
       <c r="C11" s="14"/>
       <c r="D11" s="21"/>
       <c r="E11" s="5"/>
+      <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-    </row>
-    <row r="12" spans="1:15" ht="21" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:14" ht="21" x14ac:dyDescent="0.45">
       <c r="C12" s="14"/>
       <c r="D12" s="12"/>
       <c r="E12" s="6"/>
+      <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-    </row>
-    <row r="13" spans="1:15" ht="21" x14ac:dyDescent="0.45">
+    </row>
+    <row r="13" spans="1:14" ht="21" x14ac:dyDescent="0.45">
       <c r="C13" s="14"/>
+      <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
       <c r="E14" s="15"/>
+      <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
+      <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C16" s="16"/>
       <c r="D16"/>
+      <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C17" s="16"/>
       <c r="D17"/>
       <c r="G17" s="2"/>
@@ -1262,9 +1247,8 @@
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C18" s="16"/>
       <c r="D18"/>
       <c r="G18" s="2"/>
@@ -1275,7 +1259,6 @@
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -1312,7 +1295,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -1324,40 +1307,40 @@
         <v>3</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E2" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="K2" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" s="23" t="s">
+      <c r="L2" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" s="23" t="s">
+      <c r="N2" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="K2" s="23" t="s">
+      <c r="O2" s="23" t="s">
         <v>43</v>
-      </c>
-      <c r="L2" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="M2" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="N2" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="O2" s="23" t="s">
-        <v>46</v>
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
@@ -1372,40 +1355,40 @@
         <v>5</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K3" s="23" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N3" s="23" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
@@ -1417,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D4" s="2">
         <v>4</v>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -851,7 +851,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -4,12 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
     <sheet name="#Monster" sheetId="7" r:id="rId2"/>
-    <sheet name="#MonsterPhase" sheetId="8" r:id="rId3"/>
+    <sheet name="#MonsterStat" sheetId="8" r:id="rId3"/>
+    <sheet name="#MonsterAI" sheetId="9" r:id="rId4"/>
+    <sheet name="#MonsterSpawn" sheetId="10" r:id="rId5"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="79">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="11" type="noConversion"/>
@@ -73,15 +75,7 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>!MonsterTypes</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseStatID</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -109,10 +103,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>Path</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>해골전사1-1</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -141,7 +131,38 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>BaseSkillSet</t>
+    <t>Elite</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elite</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골장군1-1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>해골 장군</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab_Monster_01</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab_BossMonster_01</t>
+  </si>
+  <si>
+    <t>Prefab_Monster_02</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>레이드보스 악마1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardGroupID</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -149,35 +170,64 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>Elite</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Elite</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골장군1-1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골 장군</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefab_Monster_01</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefab_BossMonster_01</t>
-  </si>
-  <si>
-    <t>MonsterPhase</t>
+    <t>MonsterType</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!MonsterType</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterAIType</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>AggroType</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aggressive</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Neutral</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Melee</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranged</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stationary</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boss</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>고정형</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>원거리</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>근거리</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>!</t>
+      <t>P</t>
     </r>
     <r>
       <rPr>
@@ -188,49 +238,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>int</t>
-    </r>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phase1_SkillSet</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phase1_Hp</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phase2_Hp</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phase2_SkillSet</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phase3_Hp</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phase3_SkillSet</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phase4_Hp</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phase4_SkillSet</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Phase</t>
+      <t>refab</t>
     </r>
     <r>
       <rPr>
@@ -241,40 +249,141 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Count</t>
+      <t>Path</t>
     </r>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>악마보스 페이즈별 스킬들</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phase1_to_2_TransitionSkill</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phase2_to_3_TransitionSkill</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phase3_to_4_TransitionSkill</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefab_Monster_02</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>레이드보스 악마1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterTypes</t>
+    <t>StatGroupID</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>AIGroupID</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIDs</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Skill</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseExp</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>PerLevelExp</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterStat</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>GroupID</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseValue</t>
+  </si>
+  <si>
+    <r>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>erLevel</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterAI</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>AIType</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>AggroType</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>DetectRange</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>LeashRange</t>
+  </si>
+  <si>
+    <t>선공</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>비선공</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!AggroType</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!MonsterAIType</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterID</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>RewardGroupID</t>
+  </si>
+  <si>
+    <t>!StatDetail</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatDetail_Atk_Base</t>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>GroupID</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterSpawn</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatDetailID</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -508,7 +617,7 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -561,19 +670,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -859,7 +965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="1" bestFit="1" customWidth="1"/>
@@ -870,27 +976,91 @@
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -901,22 +1071,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="10"/>
     <col min="2" max="2" width="8.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.625" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.375" customWidth="1"/>
+    <col min="10" max="10" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
@@ -924,321 +1097,324 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>17</v>
+      <c r="F2" s="19" t="s">
+        <v>46</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="N2" s="2"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>11</v>
+      <c r="C3" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>5</v>
+      <c r="E3" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4">
         <v>10001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G4">
         <v>10001</v>
       </c>
-      <c r="H4" s="20">
-        <v>10001</v>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5">
         <v>10002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G5">
         <v>10002</v>
       </c>
-      <c r="H5" s="20">
-        <v>10002</v>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6">
         <v>10003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G6">
         <v>10003</v>
       </c>
-      <c r="H6" s="20">
-        <v>10003</v>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7">
         <v>20001</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="G7">
         <v>20001</v>
       </c>
-      <c r="H7" s="20">
-        <v>20001</v>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B8" s="6">
         <v>30001</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G8">
         <v>30001</v>
       </c>
-      <c r="H8">
-        <v>30001</v>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B9" s="6">
         <v>100001</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G9">
         <v>100001</v>
       </c>
-      <c r="H9">
-        <v>100001</v>
-      </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="6"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
-    </row>
-    <row r="11" spans="1:14" ht="21" x14ac:dyDescent="0.45">
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+    </row>
+    <row r="11" spans="1:17" ht="21" x14ac:dyDescent="0.45">
       <c r="B11" s="6"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="5"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="14"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
-    </row>
-    <row r="12" spans="1:14" ht="21" x14ac:dyDescent="0.45">
-      <c r="C12" s="14"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="6"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+    </row>
+    <row r="12" spans="1:17" ht="21" x14ac:dyDescent="0.45">
+      <c r="C12" s="12"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="14"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
-    </row>
-    <row r="13" spans="1:14" ht="21" x14ac:dyDescent="0.45">
-      <c r="C13" s="14"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+    </row>
+    <row r="13" spans="1:17" ht="21" x14ac:dyDescent="0.45">
+      <c r="E13" s="14"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="15"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="12"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C16" s="16"/>
-      <c r="D16"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C16"/>
+      <c r="E16" s="16"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C17" s="16"/>
-      <c r="D17"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C17"/>
+      <c r="E17" s="16"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -1247,10 +1423,13 @@
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C18" s="16"/>
-      <c r="D18"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C18"/>
+      <c r="E18" s="16"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -1259,6 +1438,9 @@
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -1269,319 +1451,679 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="10"/>
-    <col min="2" max="2" width="8.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.875" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="2"/>
+    <col min="2" max="2" width="11.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="22" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B1" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="K2" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="L2" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="M2" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="N2" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="O2" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C2" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="19"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K3" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C3" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4">
         <v>1</v>
       </c>
+      <c r="C4">
+        <v>101</v>
+      </c>
+      <c r="D4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B8"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B9"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="7:10" x14ac:dyDescent="0.3">
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="10"/>
+    <col min="2" max="2" width="10.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="9"/>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="9"/>
+      <c r="B3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="9"/>
+      <c r="B4">
+        <v>1</v>
+      </c>
       <c r="C4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="2">
-        <v>4</v>
-      </c>
-      <c r="E4" s="2">
-        <v>100</v>
-      </c>
-      <c r="F4" s="2">
-        <v>10001</v>
-      </c>
-      <c r="H4" s="24">
-        <v>75</v>
-      </c>
-      <c r="I4" s="2">
-        <v>10002</v>
-      </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="20">
-        <v>50</v>
-      </c>
-      <c r="L4" s="2">
-        <v>10003</v>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2">
-        <v>25</v>
-      </c>
-      <c r="O4" s="2">
-        <v>10004</v>
-      </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="12">
+        <v>5</v>
+      </c>
+      <c r="F4" s="12">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6">
         <v>3</v>
       </c>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7">
         <v>4</v>
       </c>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B8" s="6">
+      <c r="C7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="22">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8">
         <v>5</v>
       </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B9" s="6"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="6"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="22">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
       <c r="B11" s="6"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="5"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="15"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="C16"/>
-      <c r="D16"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="9"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="9"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="9"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="9"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="9"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="10"/>
+    <col min="2" max="2" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="9"/>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="9"/>
+      <c r="B3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="9"/>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1001</v>
+      </c>
+      <c r="D4">
+        <v>10001</v>
+      </c>
+      <c r="E4" s="12">
+        <v>3</v>
+      </c>
+      <c r="F4" s="12">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1001</v>
+      </c>
+      <c r="D5">
+        <v>10002</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D6">
+        <v>20001</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="B7"/>
+      <c r="E7" s="22"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8"/>
+      <c r="E8" s="22"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="9"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="9"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="9"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="87">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="11" type="noConversion"/>
@@ -364,27 +364,53 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
+    <t>Normal</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>GroupID</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterSpawn</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatDetailID</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
     <t>StatDetail_Atk_Base</t>
-  </si>
-  <si>
-    <t>Normal</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>GroupID</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterSpawn</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatDetailID</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatDetail_AtkSpeed_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_CritRate_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_CritDamage_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_MaxHp_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_HpRegen_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_Def_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_MoveSpeed_Base</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Monster_MeleeAttack_01</t>
   </si>
 </sst>
 </file>
@@ -617,7 +643,7 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -680,6 +706,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1082,7 +1111,7 @@
     <col min="6" max="6" width="22.5" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.375" customWidth="1"/>
+    <col min="9" max="9" width="28.75" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.5" bestFit="1" customWidth="1"/>
@@ -1190,13 +1219,19 @@
         <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G4">
-        <v>10001</v>
+        <v>101</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="J4">
+        <v>10</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -1223,7 +1258,11 @@
         <v>26</v>
       </c>
       <c r="G5">
-        <v>10002</v>
+        <v>101</v>
+      </c>
+      <c r="I5" s="24"/>
+      <c r="J5">
+        <v>10</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -1250,7 +1289,11 @@
         <v>26</v>
       </c>
       <c r="G6">
-        <v>10003</v>
+        <v>101</v>
+      </c>
+      <c r="I6" s="24"/>
+      <c r="J6">
+        <v>15</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -1277,7 +1320,11 @@
         <v>28</v>
       </c>
       <c r="G7">
-        <v>20001</v>
+        <v>101</v>
+      </c>
+      <c r="I7" s="24"/>
+      <c r="J7">
+        <v>50</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -1303,7 +1350,11 @@
         <v>27</v>
       </c>
       <c r="G8">
-        <v>30001</v>
+        <v>101</v>
+      </c>
+      <c r="I8" s="24"/>
+      <c r="J8">
+        <v>100</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -1329,7 +1380,11 @@
         <v>27</v>
       </c>
       <c r="G9">
-        <v>100001</v>
+        <v>101</v>
+      </c>
+      <c r="I9" s="24"/>
+      <c r="J9">
+        <v>500</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -1457,7 +1512,7 @@
     <col min="1" max="1" width="9" style="10"/>
     <col min="2" max="2" width="11.875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.25" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.5" style="2" customWidth="1"/>
     <col min="7" max="7" width="8.375" bestFit="1" customWidth="1"/>
@@ -1485,7 +1540,7 @@
         <v>54</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
         <v>57</v>
@@ -1527,14 +1582,14 @@
       <c r="C4">
         <v>101</v>
       </c>
-      <c r="D4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4">
+      <c r="D4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="2">
         <v>10</v>
       </c>
-      <c r="F4">
-        <v>1</v>
+      <c r="F4" s="2">
+        <v>2</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -1542,79 +1597,141 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
-      <c r="B5"/>
-      <c r="C5"/>
-      <c r="D5"/>
-      <c r="E5"/>
-      <c r="F5"/>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>101</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
-      <c r="B6"/>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>101</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
-      <c r="B7"/>
-      <c r="C7"/>
-      <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7"/>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>101</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B8"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>101</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="2">
+        <v>300</v>
+      </c>
+      <c r="F8" s="2">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B9"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>101</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="2">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>101</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="2">
+        <v>5</v>
+      </c>
+      <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>101</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -1925,7 +2042,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
@@ -1937,7 +2054,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
         <v>68</v>
@@ -1959,7 +2076,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>55</v>
@@ -2001,37 +2118,23 @@
         <v>2</v>
       </c>
       <c r="C5" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D5">
-        <v>10002</v>
+        <v>20001</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1002</v>
-      </c>
-      <c r="D6">
-        <v>20001</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
+      <c r="B6"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
@@ -2067,8 +2170,7 @@
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
+      <c r="C11"/>
       <c r="E11" s="6"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -2076,14 +2178,14 @@
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
+      <c r="C12"/>
       <c r="E12" s="6"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
+      <c r="C13"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -34,10 +34,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="89">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
@@ -56,31 +56,31 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Monster</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Boss</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>MonsterType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>악마1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>악마</t>
@@ -100,130 +100,130 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>해골전사1-1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>해골궁수1-1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>해골마법사1-1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>해골 궁수</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>해골 전사</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>해골 마법사</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Elite</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Elite</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>해골장군1-1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>해골 장군</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_Monster_01</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_BossMonster_01</t>
   </si>
   <si>
     <t>Prefab_Monster_02</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>레이드보스 악마1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>RewardGroupID</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>MonsterType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!MonsterType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>MonsterAIType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>AggroType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Aggressive</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Neutral</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Melee</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Ranged</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Stationary</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Boss</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>고정형</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>보스</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>원거리</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>근거리</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -251,47 +251,47 @@
       </rPr>
       <t>Path</t>
     </r>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>StatGroupID</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>AIGroupID</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>SkillIDs</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!Skill</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>BaseExp</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>PerLevelExp</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>MonsterStat</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>GroupID</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>BaseValue</t>
@@ -310,42 +310,42 @@
       </rPr>
       <t>erLevel</t>
     </r>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>MonsterAI</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>AIType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>AggroType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>DetectRange</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>LeashRange</t>
   </si>
   <si>
     <t>선공</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>비선공</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!AggroType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!MonsterAIType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>MonsterID</t>
@@ -361,76 +361,76 @@
   </si>
   <si>
     <t>!StatDetail</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>GroupID</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatDetailID</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatDetail_Atk_Base</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatDetail_AtkSpeed_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_CritRate_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_CritDamage_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_MaxHp_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_HpRegen_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_Def_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_MoveSpeed_Base</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Monster_MeleeAttack_01</t>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>RespawnTime</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>MonsterSpawn</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatDetailID</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatDetail_Atk_Base</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatDetail_AtkSpeed_Base</t>
-  </si>
-  <si>
-    <t>StatDetail_CritRate_Base</t>
-  </si>
-  <si>
-    <t>StatDetail_CritDamage_Base</t>
-  </si>
-  <si>
-    <t>StatDetail_MaxHp_Base</t>
-  </si>
-  <si>
-    <t>StatDetail_HpRegen_Base</t>
-  </si>
-  <si>
-    <t>StatDetail_Def_Base</t>
-  </si>
-  <si>
-    <t>StatDetail_MoveSpeed_Base</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_Monster_MeleeAttack_01</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -635,13 +635,13 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -657,46 +657,46 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -705,10 +705,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -986,7 +986,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1093,7 +1093,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1227,8 +1227,8 @@
       <c r="G4">
         <v>101</v>
       </c>
-      <c r="I4" s="24" t="s">
-        <v>86</v>
+      <c r="I4" s="23" t="s">
+        <v>85</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -1260,7 +1260,7 @@
       <c r="G5">
         <v>101</v>
       </c>
-      <c r="I5" s="24"/>
+      <c r="I5" s="23"/>
       <c r="J5">
         <v>10</v>
       </c>
@@ -1291,7 +1291,7 @@
       <c r="G6">
         <v>101</v>
       </c>
-      <c r="I6" s="24"/>
+      <c r="I6" s="23"/>
       <c r="J6">
         <v>15</v>
       </c>
@@ -1322,7 +1322,7 @@
       <c r="G7">
         <v>101</v>
       </c>
-      <c r="I7" s="24"/>
+      <c r="I7" s="23"/>
       <c r="J7">
         <v>50</v>
       </c>
@@ -1352,7 +1352,7 @@
       <c r="G8">
         <v>101</v>
       </c>
-      <c r="I8" s="24"/>
+      <c r="I8" s="23"/>
       <c r="J8">
         <v>100</v>
       </c>
@@ -1382,7 +1382,7 @@
       <c r="G9">
         <v>101</v>
       </c>
-      <c r="I9" s="24"/>
+      <c r="I9" s="23"/>
       <c r="J9">
         <v>500</v>
       </c>
@@ -1498,7 +1498,7 @@
       <c r="Q18" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1540,7 +1540,7 @@
         <v>54</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
         <v>57</v>
@@ -1583,7 +1583,7 @@
         <v>101</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E4" s="2">
         <v>10</v>
@@ -1604,7 +1604,7 @@
         <v>101</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -1622,7 +1622,7 @@
         <v>101</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" s="2">
         <v>0.1</v>
@@ -1641,7 +1641,7 @@
         <v>101</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E7" s="2">
         <v>1.5</v>
@@ -1659,7 +1659,7 @@
         <v>101</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E8" s="2">
         <v>300</v>
@@ -1680,7 +1680,7 @@
         <v>101</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
@@ -1702,7 +1702,7 @@
         <v>101</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
@@ -1720,7 +1720,7 @@
         <v>101</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
@@ -1769,7 +1769,7 @@
       <c r="J18" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -2017,14 +2017,14 @@
       <c r="A22" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="10"/>
@@ -2033,22 +2033,23 @@
     <col min="4" max="4" width="10.375" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5.75" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="23" t="s">
-        <v>76</v>
+      <c r="B1" s="24" t="s">
+        <v>88</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
       <c r="E1" s="20"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="6" t="s">
         <v>2</v>
@@ -2066,11 +2067,14 @@
         <v>70</v>
       </c>
       <c r="G2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H2" t="s">
         <v>71</v>
       </c>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="12" t="s">
         <v>6</v>
@@ -2088,11 +2092,14 @@
         <v>55</v>
       </c>
       <c r="G3" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4">
         <v>1</v>
@@ -2109,10 +2116,13 @@
       <c r="F4" s="12">
         <v>3</v>
       </c>
-      <c r="G4" s="2"/>
+      <c r="G4" s="12">
+        <v>3</v>
+      </c>
       <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5">
         <v>2</v>
@@ -2129,103 +2139,108 @@
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="G5">
+        <v>3</v>
+      </c>
       <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6"/>
-      <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7"/>
       <c r="E7" s="22"/>
-      <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8"/>
       <c r="E8" s="22"/>
-      <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
-      <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
-      <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="6"/>
       <c r="C11"/>
       <c r="E11" s="6"/>
-      <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
       <c r="B12" s="6"/>
       <c r="C12"/>
       <c r="E12" s="6"/>
-      <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
       <c r="C13"/>
-      <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
-      <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
-      <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
-      <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
-      <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -37,7 +37,7 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="89">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
@@ -56,31 +56,31 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Monster</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Boss</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>MonsterType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>악마1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>악마</t>
@@ -100,130 +100,130 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>해골전사1-1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>해골궁수1-1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>해골마법사1-1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>해골 궁수</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>해골 전사</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>해골 마법사</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Elite</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Elite</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>해골장군1-1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>해골 장군</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_Monster_01</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_BossMonster_01</t>
   </si>
   <si>
     <t>Prefab_Monster_02</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>레이드보스 악마1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>RewardGroupID</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>MonsterType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!MonsterType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>MonsterAIType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>AggroType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Aggressive</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Neutral</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Melee</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Ranged</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Stationary</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Boss</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>고정형</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>보스</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>원거리</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>근거리</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -251,47 +251,47 @@
       </rPr>
       <t>Path</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>StatGroupID</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>AIGroupID</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>SkillIDs</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!Skill</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>BaseExp</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>PerLevelExp</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>MonsterStat</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>GroupID</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>BaseValue</t>
@@ -310,42 +310,42 @@
       </rPr>
       <t>erLevel</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>MonsterAI</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>AIType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>AggroType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>DetectRange</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>LeashRange</t>
   </si>
   <si>
     <t>선공</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>비선공</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!AggroType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!MonsterAIType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>MonsterID</t>
@@ -361,27 +361,27 @@
   </si>
   <si>
     <t>!StatDetail</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>GroupID</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>StatDetailID</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>StatDetail_Atk_Base</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>StatDetail_AtkSpeed_Base</t>
@@ -403,34 +403,42 @@
   </si>
   <si>
     <t>StatDetail_MoveSpeed_Base</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Skill_Monster_MeleeAttack_01</t>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterSpawn</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>RespawnTime</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterSpawn</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -635,13 +643,13 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -657,46 +665,46 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -705,10 +713,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -986,7 +994,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1093,7 +1101,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1498,7 +1506,7 @@
       <c r="Q18" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1769,7 +1777,7 @@
       <c r="J18" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -2017,7 +2025,7 @@
       <c r="A22" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2043,7 +2051,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
@@ -2067,7 +2075,7 @@
         <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H2" t="s">
         <v>71</v>
@@ -2117,7 +2125,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="12">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -2140,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -2240,7 +2248,7 @@
       <c r="A20" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -4,14 +4,13 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="4"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
     <sheet name="#Monster" sheetId="7" r:id="rId2"/>
     <sheet name="#MonsterStat" sheetId="8" r:id="rId3"/>
-    <sheet name="#MonsterAI" sheetId="9" r:id="rId4"/>
-    <sheet name="#MonsterSpawn" sheetId="10" r:id="rId5"/>
+    <sheet name="#MonsterSpawn" sheetId="10" r:id="rId4"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="89">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="11" type="noConversion"/>
@@ -103,18 +102,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>해골전사1-1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골궁수1-1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골마법사1-1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>해골 궁수</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -139,10 +126,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>해골장군1-1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>해골 장군</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -155,10 +138,6 @@
   </si>
   <si>
     <t>Prefab_Monster_02</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>레이드보스 악마1</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -258,10 +237,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>AIGroupID</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>SkillIDs</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -313,18 +288,10 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>MonsterAI</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>AIType</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>AggroType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>DetectRange</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -418,6 +385,38 @@
   </si>
   <si>
     <t>RespawnTime</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranged</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Monster_RangeAttack_01</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Monster_CastAttack_01</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Monster_MeleeAttack_01</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>고블린 전사1-1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>고블린 궁수1-1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>고블린 법사1-1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>고블린 장군1-1</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -1018,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -1028,7 +1027,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1041,39 +1040,39 @@
         <v>0</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1081,23 +1080,23 @@
         <v>0</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1108,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="10"/>
@@ -1118,15 +1117,16 @@
     <col min="5" max="5" width="14.125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.5" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="2"/>
+    <col min="8" max="8" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="12.25" customWidth="1"/>
+    <col min="12" max="12" width="28.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="6" t="s">
         <v>2</v>
@@ -1149,32 +1149,41 @@
         <v>10</v>
       </c>
       <c r="F2" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="N2" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="G2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
+      <c r="O2" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="Q2" s="2"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="12" t="s">
         <v>6</v>
@@ -1186,7 +1195,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>14</v>
@@ -1194,154 +1203,217 @@
       <c r="G3" t="s">
         <v>11</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="N3" t="s">
         <v>11</v>
       </c>
-      <c r="K3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
+      <c r="O3" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4">
         <v>10001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G4">
         <v>101</v>
       </c>
-      <c r="I4" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="J4">
+      <c r="H4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="12">
+        <v>3</v>
+      </c>
+      <c r="K4" s="12">
         <v>10</v>
       </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
+      <c r="L4" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="M4">
+        <v>10</v>
+      </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5">
         <v>10002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G5">
         <v>101</v>
       </c>
-      <c r="I5" s="23"/>
+      <c r="H5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="12">
         <v>10</v>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
+      <c r="L5" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="M5">
+        <v>10</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6">
         <v>10003</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G6">
         <v>101</v>
       </c>
-      <c r="I6" s="23"/>
+      <c r="H6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6" s="12">
+        <v>10</v>
+      </c>
+      <c r="L6" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="M6">
         <v>15</v>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7">
         <v>20001</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="G7">
         <v>101</v>
       </c>
-      <c r="I7" s="23"/>
+      <c r="H7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="M7">
         <v>50</v>
       </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B8" s="6">
         <v>30001</v>
       </c>
@@ -1355,127 +1427,125 @@
         <v>9</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G8">
         <v>101</v>
       </c>
-      <c r="I8" s="23"/>
-      <c r="J8">
+      <c r="H8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="22">
+        <v>5</v>
+      </c>
+      <c r="K8">
+        <v>8</v>
+      </c>
+      <c r="L8" s="23"/>
+      <c r="M8">
         <v>100</v>
       </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B9" s="6">
-        <v>100001</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9">
-        <v>101</v>
-      </c>
-      <c r="I9" s="23"/>
-      <c r="J9">
-        <v>500</v>
-      </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B9" s="6"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="22"/>
+      <c r="L9" s="23"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="6"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
-    </row>
-    <row r="11" spans="1:17" ht="21" x14ac:dyDescent="0.45">
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+    </row>
+    <row r="11" spans="1:20" ht="21" x14ac:dyDescent="0.45">
       <c r="B11" s="6"/>
       <c r="C11" s="18"/>
       <c r="D11" s="5"/>
       <c r="E11" s="14"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
-    </row>
-    <row r="12" spans="1:17" ht="21" x14ac:dyDescent="0.45">
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+    </row>
+    <row r="12" spans="1:20" ht="21" x14ac:dyDescent="0.45">
       <c r="C12" s="12"/>
       <c r="D12" s="6"/>
       <c r="E12" s="14"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+      <c r="L12" s="23"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
-    </row>
-    <row r="13" spans="1:17" ht="21" x14ac:dyDescent="0.45">
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+    </row>
+    <row r="13" spans="1:20" ht="21" x14ac:dyDescent="0.45">
       <c r="E13" s="14"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
+      <c r="L13" s="23"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C14" s="12"/>
       <c r="D14" s="15"/>
       <c r="E14" s="12"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
+      <c r="L14" s="23"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C16"/>
       <c r="E16" s="16"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C17"/>
       <c r="E17" s="16"/>
       <c r="G17" s="2"/>
@@ -1489,8 +1559,11 @@
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C18"/>
       <c r="E18" s="16"/>
       <c r="G18" s="2"/>
@@ -1504,6 +1577,9 @@
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -1532,7 +1608,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
@@ -1545,16 +1621,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G2" s="19"/>
       <c r="H2" s="2"/>
@@ -1567,16 +1643,16 @@
         <v>6</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -1591,7 +1667,7 @@
         <v>101</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E4" s="2">
         <v>10</v>
@@ -1612,7 +1688,7 @@
         <v>101</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -1630,7 +1706,7 @@
         <v>101</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E6" s="2">
         <v>0.1</v>
@@ -1649,7 +1725,7 @@
         <v>101</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E7" s="2">
         <v>1.5</v>
@@ -1667,10 +1743,10 @@
         <v>101</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E8" s="2">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="F8" s="2">
         <v>10</v>
@@ -1688,7 +1764,7 @@
         <v>101</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
@@ -1710,7 +1786,7 @@
         <v>101</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
@@ -1728,7 +1804,7 @@
         <v>101</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
@@ -1785,254 +1861,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9" style="10"/>
-    <col min="2" max="2" width="10.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="9"/>
-      <c r="B2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="12">
-        <v>5</v>
-      </c>
-      <c r="F4" s="12">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>10</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="22">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>8</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="22">
-        <v>3</v>
-      </c>
-      <c r="F8">
-        <v>15</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B10"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="9"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="10"/>
@@ -2051,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
@@ -2063,22 +1892,22 @@
         <v>2</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="I2" s="2"/>
     </row>
@@ -2088,22 +1917,22 @@
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="I3" s="2"/>
     </row>
@@ -2122,10 +1951,10 @@
         <v>3</v>
       </c>
       <c r="F4" s="12">
-        <v>3</v>
-      </c>
-      <c r="G4" s="12">
         <v>15</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -2139,49 +1968,113 @@
         <v>1002</v>
       </c>
       <c r="D5">
-        <v>20001</v>
-      </c>
-      <c r="E5">
+        <v>10001</v>
+      </c>
+      <c r="E5" s="12">
         <v>5</v>
       </c>
-      <c r="F5">
-        <v>1</v>
+      <c r="F5" s="12">
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
-      <c r="B6"/>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D6">
+        <v>10002</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
-      <c r="B7"/>
-      <c r="E7" s="22"/>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1003</v>
+      </c>
+      <c r="D7">
+        <v>10001</v>
+      </c>
+      <c r="E7" s="2">
+        <v>10</v>
+      </c>
+      <c r="F7" s="22">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
-      <c r="B8"/>
-      <c r="E8" s="22"/>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1003</v>
+      </c>
+      <c r="D8">
+        <v>10002</v>
+      </c>
+      <c r="E8" s="2">
+        <v>10</v>
+      </c>
+      <c r="F8" s="22">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
+      <c r="A9" s="9"/>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1003</v>
+      </c>
+      <c r="D9">
+        <v>10003</v>
+      </c>
+      <c r="E9" s="2">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B10"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -2189,9 +2082,9 @@
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="6"/>
-      <c r="C11"/>
+      <c r="B11"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -2206,17 +2099,22 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
+      <c r="B13" s="6"/>
       <c r="C13"/>
+      <c r="D13"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
+      <c r="C14"/>
+      <c r="D14"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
+      <c r="D15"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
@@ -2227,13 +2125,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
+      <c r="D17"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+      <c r="D18"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
@@ -2246,6 +2144,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -993,7 +993,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1260,7 +1260,7 @@
         <v>31</v>
       </c>
       <c r="J4" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K4" s="12">
         <v>10</v>
@@ -1305,7 +1305,7 @@
         <v>31</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5" s="12">
         <v>10</v>
@@ -1350,7 +1350,7 @@
         <v>31</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K6" s="12">
         <v>10</v>
@@ -1395,7 +1395,7 @@
         <v>32</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -1746,7 +1746,7 @@
         <v>73</v>
       </c>
       <c r="E8" s="2">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="F8" s="2">
         <v>10</v>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -1,47 +1,86 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="#Enum" sheetId="6" r:id="rId1"/>
-    <sheet name="#Monster" sheetId="7" r:id="rId2"/>
-    <sheet name="#MonsterStat" sheetId="8" r:id="rId3"/>
-    <sheet name="#MonsterSpawn" sheetId="10" r:id="rId4"/>
+    <sheet name="#Enum" sheetId="1" r:id="rId1"/>
+    <sheet name="#Monster" sheetId="2" r:id="rId2"/>
+    <sheet name="#MonsterStat" sheetId="3" r:id="rId3"/>
+    <sheet name="#MonsterSpawn" sheetId="4" r:id="rId4"/>
+    <sheet name="#BossMonsterPhase" sheetId="5" r:id="rId5"/>
+    <sheet name="#MonsterSkillSet" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="145621"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="89">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterType</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Elite</t>
+  </si>
+  <si>
+    <t>Boss</t>
+  </si>
+  <si>
+    <t>MonsterAIType</t>
+  </si>
+  <si>
+    <t>Melee</t>
+  </si>
+  <si>
+    <t>근거리</t>
+  </si>
+  <si>
+    <t>Ranged</t>
+  </si>
+  <si>
+    <t>원거리</t>
+  </si>
+  <si>
+    <t>Stationary</t>
+  </si>
+  <si>
+    <t>고정형</t>
+  </si>
+  <si>
+    <t>보스</t>
+  </si>
+  <si>
+    <t>AggroType</t>
+  </si>
+  <si>
+    <t>Aggressive</t>
+  </si>
+  <si>
+    <t>선공</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>비선공</t>
   </si>
   <si>
     <t>!Table</t>
   </si>
   <si>
+    <t>Monster</t>
+  </si>
+  <si>
     <t>!ID</t>
   </si>
   <si>
@@ -51,393 +90,214 @@
     <t>Desc</t>
   </si>
   <si>
+    <t>PrefabPath</t>
+  </si>
+  <si>
+    <t>StatGroupID</t>
+  </si>
+  <si>
+    <t>AIType</t>
+  </si>
+  <si>
+    <t>DetectRange</t>
+  </si>
+  <si>
+    <t>LeashRange</t>
+  </si>
+  <si>
+    <t>SkillSetGroupID</t>
+  </si>
+  <si>
+    <t>BaseExp</t>
+  </si>
+  <si>
+    <t>PerLevelExp</t>
+  </si>
+  <si>
+    <t>RewardGroupID</t>
+  </si>
+  <si>
+    <t>!int</t>
+  </si>
+  <si>
     <t>!string</t>
   </si>
   <si>
-    <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monster</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Normal</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Boss</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <t>!MonsterType</t>
+  </si>
+  <si>
+    <t>!MonsterAIType</t>
+  </si>
+  <si>
+    <t>!AggroType</t>
+  </si>
+  <si>
+    <t>!float</t>
+  </si>
+  <si>
+    <t>고블린 전사1-1</t>
+  </si>
+  <si>
+    <t>해골 전사</t>
+  </si>
+  <si>
+    <t>Prefab_Monster_01</t>
+  </si>
+  <si>
+    <t>고블린 궁수1-1</t>
+  </si>
+  <si>
+    <t>해골 궁수</t>
+  </si>
+  <si>
+    <t>Prefab_Monster_02</t>
+  </si>
+  <si>
+    <t>고블린 법사1-1</t>
+  </si>
+  <si>
+    <t>해골 마법사</t>
+  </si>
+  <si>
+    <t>Prefab_Monster_03</t>
+  </si>
+  <si>
+    <t>고블린 장군1-1</t>
+  </si>
+  <si>
+    <t>해골 장군</t>
+  </si>
+  <si>
+    <t>Prefab_Monster_04</t>
   </si>
   <si>
     <t>악마1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>악마</t>
   </si>
   <si>
-    <r>
-      <t>!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>string</t>
-    </r>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골 궁수</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골 전사</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골 마법사</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Normal</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Elite</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Elite</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>해골 장군</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefab_Monster_01</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>Prefab_BossMonster_01</t>
   </si>
   <si>
-    <t>Prefab_Monster_02</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>RewardGroupID</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>!MonsterType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterAIType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>AggroType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Aggressive</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Neutral</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Melee</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ranged</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stationary</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Boss</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>고정형</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>보스</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>원거리</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>근거리</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>refab</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Path</t>
-    </r>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatGroupID</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillIDs</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <t>MonsterStat</t>
+  </si>
+  <si>
+    <t>GroupID</t>
+  </si>
+  <si>
+    <t>StatDetailID</t>
+  </si>
+  <si>
+    <t>BaseValue</t>
+  </si>
+  <si>
+    <t>PerLevel</t>
+  </si>
+  <si>
+    <t>!StatDetail</t>
+  </si>
+  <si>
+    <t>StatDetail_Atk_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_AtkSpeed_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_CritRate_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_CritDamage_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_MaxHp_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_HpRegen_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_Def_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_MoveSpeed_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_MaxBreakGauge_Base</t>
+  </si>
+  <si>
+    <t>MonsterSpawn</t>
+  </si>
+  <si>
+    <t>MonsterID</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>RespawnTime</t>
+  </si>
+  <si>
+    <t>BossMonsterPhase</t>
+  </si>
+  <si>
+    <t>PhaseOrder</t>
+  </si>
+  <si>
+    <t>HpThreshold</t>
+  </si>
+  <si>
+    <t>PhaseSkillID</t>
+  </si>
+  <si>
+    <t>GimmickCount</t>
+  </si>
+  <si>
+    <t>GimmickRequired</t>
+  </si>
+  <si>
+    <t>GimmickRadius</t>
   </si>
   <si>
     <t>!Skill</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseExp</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>PerLevelExp</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterStat</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>GroupID</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseValue</t>
-  </si>
-  <si>
-    <r>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>erLevel</t>
-    </r>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>AIType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>DetectRange</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>LeashRange</t>
-  </si>
-  <si>
-    <t>선공</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>비선공</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>!AggroType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>!MonsterAIType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterID</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>RewardGroupID</t>
-  </si>
-  <si>
-    <t>!StatDetail</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Normal</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>GroupID</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatDetailID</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatDetail_Atk_Base</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatDetail_AtkSpeed_Base</t>
-  </si>
-  <si>
-    <t>StatDetail_CritRate_Base</t>
-  </si>
-  <si>
-    <t>StatDetail_CritDamage_Base</t>
-  </si>
-  <si>
-    <t>StatDetail_MaxHp_Base</t>
-  </si>
-  <si>
-    <t>StatDetail_HpRegen_Base</t>
-  </si>
-  <si>
-    <t>StatDetail_Def_Base</t>
-  </si>
-  <si>
-    <t>StatDetail_MoveSpeed_Base</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Monster_Boss_Doom_01</t>
+  </si>
+  <si>
+    <t>MonsterSkillSet</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>SkillID</t>
   </si>
   <si>
     <t>Skill_Monster_MeleeAttack_01</t>
   </si>
   <si>
-    <t>!float</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterSpawn</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>RespawnTime</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ranged</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>Skill_Monster_RangeAttack_01</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>Skill_Monster_CastAttack_01</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_Monster_MeleeAttack_01</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린 전사1-1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린 궁수1-1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린 법사1-1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린 장군1-1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Monster_OrcGeneral_Active_01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -512,13 +372,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="맑은 고딕"/>
@@ -574,7 +427,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -639,18 +492,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -664,58 +528,55 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -730,9 +591,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1009,7 +867,8 @@
     <col min="3" max="3" width="11" style="2" customWidth="1"/>
     <col min="4" max="4" width="11.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="11.375" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="6" max="9" width="9" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1017,22 +876,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1040,39 +899,39 @@
         <v>0</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1080,27 +939,27 @@
         <v>0</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1110,7 +969,7 @@
   <dimension ref="A1:T18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="10"/>
+    <col min="1" max="1" width="9" style="23" customWidth="1"/>
     <col min="2" max="2" width="8.5" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.625" style="2" bestFit="1" customWidth="1"/>
@@ -1119,64 +978,66 @@
     <col min="7" max="7" width="12.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.25" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="12.25" customWidth="1"/>
-    <col min="12" max="12" width="28.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="2"/>
+    <col min="16" max="20" width="9" customWidth="1"/>
+    <col min="21" max="24" width="9" style="2" customWidth="1"/>
+    <col min="25" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>7</v>
+    <row r="1" spans="1:20" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="9"/>
+      <c r="A2" s="8"/>
       <c r="B2" s="6" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>41</v>
+        <v>22</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I2" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="K2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L2" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="N2" s="19" t="s">
-        <v>46</v>
-      </c>
       <c r="O2" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -1184,48 +1045,48 @@
       <c r="T2" s="2"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="12" t="s">
-        <v>6</v>
+      <c r="A3" s="8"/>
+      <c r="B3" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>14</v>
+        <v>33</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>44</v>
+        <v>32</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>32</v>
       </c>
       <c r="M3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="N3" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
@@ -1234,39 +1095,39 @@
       <c r="T3" s="2"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
+      <c r="A4" s="8"/>
       <c r="B4">
         <v>10001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G4">
         <v>101</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="12">
-        <v>5</v>
-      </c>
-      <c r="K4" s="12">
+        <v>14</v>
+      </c>
+      <c r="J4" s="18">
+        <v>3</v>
+      </c>
+      <c r="K4" s="18">
         <v>10</v>
       </c>
-      <c r="L4" s="23" t="s">
-        <v>84</v>
+      <c r="L4" s="19">
+        <v>1001</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -1279,39 +1140,39 @@
       <c r="T4" s="2"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
+      <c r="A5" s="8"/>
       <c r="B5">
         <v>10002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="G5">
         <v>101</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5" s="12">
+        <v>3</v>
+      </c>
+      <c r="K5" s="18">
         <v>10</v>
       </c>
-      <c r="L5" s="23" t="s">
-        <v>82</v>
+      <c r="L5" s="19">
+        <v>1002</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -1324,39 +1185,39 @@
       <c r="T5" s="2"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
+      <c r="A6" s="8"/>
       <c r="B6">
         <v>10003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="G6">
         <v>101</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6" s="12">
+        <v>3</v>
+      </c>
+      <c r="K6" s="18">
         <v>10</v>
       </c>
-      <c r="L6" s="23" t="s">
-        <v>83</v>
+      <c r="L6" s="19">
+        <v>1003</v>
       </c>
       <c r="M6">
         <v>15</v>
@@ -1369,30 +1230,30 @@
       <c r="T6" s="2"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
+      <c r="A7" s="8"/>
       <c r="B7">
         <v>20001</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G7">
-        <v>101</v>
+        <v>20001</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -1400,8 +1261,8 @@
       <c r="K7">
         <v>10</v>
       </c>
-      <c r="L7" s="23" t="s">
-        <v>77</v>
+      <c r="L7" s="19">
+        <v>2001</v>
       </c>
       <c r="M7">
         <v>50</v>
@@ -1418,33 +1279,35 @@
         <v>30001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G8">
-        <v>101</v>
+        <v>30001</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="22">
+        <v>16</v>
+      </c>
+      <c r="J8" s="18">
         <v>5</v>
       </c>
       <c r="K8">
         <v>8</v>
       </c>
-      <c r="L8" s="23"/>
+      <c r="L8" s="19">
+        <v>3000</v>
+      </c>
       <c r="M8">
         <v>100</v>
       </c>
@@ -1459,8 +1322,8 @@
       <c r="B9" s="6"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
-      <c r="J9" s="22"/>
-      <c r="L9" s="23"/>
+      <c r="J9" s="18"/>
+      <c r="L9" s="19"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
@@ -1469,7 +1332,7 @@
       <c r="T9" s="2"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
+      <c r="A10" s="8"/>
       <c r="B10" s="6"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
@@ -1478,11 +1341,11 @@
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:20" ht="21" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="6"/>
-      <c r="C11" s="18"/>
+      <c r="C11" s="15"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="14"/>
+      <c r="E11" s="11"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
@@ -1490,11 +1353,11 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:20" ht="21" x14ac:dyDescent="0.45">
-      <c r="C12" s="12"/>
+    <row r="12" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C12" s="18"/>
       <c r="D12" s="6"/>
-      <c r="E12" s="14"/>
-      <c r="L12" s="23"/>
+      <c r="E12" s="11"/>
+      <c r="L12" s="19"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
@@ -1502,9 +1365,9 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:20" ht="21" x14ac:dyDescent="0.45">
-      <c r="E13" s="14"/>
-      <c r="L13" s="23"/>
+    <row r="13" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E13" s="11"/>
+      <c r="L13" s="19"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
@@ -1513,10 +1376,10 @@
       <c r="T13" s="2"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="C14" s="12"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="12"/>
-      <c r="L14" s="23"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="18"/>
+      <c r="L14" s="19"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
@@ -1525,9 +1388,9 @@
       <c r="T14" s="2"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
@@ -1536,8 +1399,7 @@
       <c r="T15" s="2"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="C16"/>
-      <c r="E16" s="16"/>
+      <c r="E16" s="13"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
@@ -1545,9 +1407,8 @@
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
     </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C17"/>
-      <c r="E17" s="16"/>
+    <row r="17" spans="5:20" x14ac:dyDescent="0.3">
+      <c r="E17" s="13"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -1563,9 +1424,8 @@
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.3">
-      <c r="C18"/>
-      <c r="E18" s="16"/>
+    <row r="18" spans="5:20" x14ac:dyDescent="0.3">
+      <c r="E18" s="13"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -1582,84 +1442,86 @@
       <c r="T18" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="10"/>
+    <col min="1" max="1" width="9" style="23" customWidth="1"/>
     <col min="2" max="2" width="11.875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.25" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.25" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.5" style="2" customWidth="1"/>
     <col min="7" max="7" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="8" max="10" width="9" customWidth="1"/>
+    <col min="11" max="14" width="9" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+    <row r="1" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="9"/>
+      <c r="A2" s="8"/>
       <c r="B2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>68</v>
+        <v>20</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>55</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G2" s="19"/>
+        <v>56</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="16"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>50</v>
+      <c r="A3" s="8"/>
+      <c r="B3" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>37</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
+      <c r="A4" s="8"/>
       <c r="B4">
         <v>1</v>
       </c>
@@ -1667,7 +1529,7 @@
         <v>101</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E4" s="2">
         <v>10</v>
@@ -1680,7 +1542,7 @@
       <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
+      <c r="A5" s="8"/>
       <c r="B5">
         <v>2</v>
       </c>
@@ -1688,7 +1550,7 @@
         <v>101</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -1698,7 +1560,7 @@
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
+      <c r="A6" s="8"/>
       <c r="B6">
         <v>3</v>
       </c>
@@ -1706,7 +1568,7 @@
         <v>101</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E6" s="2">
         <v>0.1</v>
@@ -1717,7 +1579,7 @@
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
+      <c r="A7" s="8"/>
       <c r="B7">
         <v>4</v>
       </c>
@@ -1725,7 +1587,7 @@
         <v>101</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E7" s="2">
         <v>1.5</v>
@@ -1743,7 +1605,7 @@
         <v>101</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E8" s="2">
         <v>250</v>
@@ -1764,7 +1626,7 @@
         <v>101</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E9" s="2">
         <v>5</v>
@@ -1778,7 +1640,7 @@
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
+      <c r="A10" s="8"/>
       <c r="B10">
         <v>7</v>
       </c>
@@ -1786,7 +1648,7 @@
         <v>101</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
@@ -1804,7 +1666,7 @@
         <v>101</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
@@ -1815,56 +1677,312 @@
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>20001</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="2">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2">
+        <v>2</v>
+      </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>20001</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14">
+        <v>20001</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.1</v>
+      </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>20001</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1.5</v>
+      </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>20001</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2500</v>
+      </c>
+      <c r="F16" s="2">
+        <v>10</v>
+      </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
     </row>
-    <row r="17" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>20001</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="2">
+        <v>5</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
     </row>
-    <row r="18" spans="7:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>20001</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="2">
+        <v>5</v>
+      </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
     </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>16</v>
+      </c>
+      <c r="C19">
+        <v>20001</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>17</v>
+      </c>
+      <c r="C20">
+        <v>20001</v>
+      </c>
+      <c r="D20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>18</v>
+      </c>
+      <c r="C21">
+        <v>30001</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="2">
+        <v>10</v>
+      </c>
+      <c r="F21" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>19</v>
+      </c>
+      <c r="C22">
+        <v>30001</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>30001</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>21</v>
+      </c>
+      <c r="C24">
+        <v>30001</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B25">
+        <v>22</v>
+      </c>
+      <c r="C25">
+        <v>30001</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="2">
+        <v>25000</v>
+      </c>
+      <c r="F25" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <v>23</v>
+      </c>
+      <c r="C26">
+        <v>30001</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="2">
+        <v>5</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B27">
+        <v>24</v>
+      </c>
+      <c r="C27">
+        <v>30001</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B28">
+        <v>25</v>
+      </c>
+      <c r="C28">
+        <v>30001</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B29">
+        <v>26</v>
+      </c>
+      <c r="C29">
+        <v>30001</v>
+      </c>
+      <c r="D29" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29">
+        <v>300</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="10"/>
+    <col min="1" max="1" width="9" style="23" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="10.375" style="2" bestFit="1" customWidth="1"/>
@@ -1872,72 +1990,74 @@
     <col min="6" max="6" width="6.75" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="13" width="9" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
+    <row r="1" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="9"/>
+      <c r="A2" s="8"/>
       <c r="B2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>66</v>
+        <v>20</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="G2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H2" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="12" t="s">
-        <v>6</v>
+      <c r="A3" s="8"/>
+      <c r="B3" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>49</v>
+        <v>32</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
+      <c r="A4" s="8"/>
       <c r="B4">
         <v>1</v>
       </c>
@@ -1947,80 +2067,80 @@
       <c r="D4">
         <v>10001</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="18">
+        <v>1</v>
+      </c>
+      <c r="F4" s="18">
         <v>3</v>
       </c>
-      <c r="F4" s="12">
-        <v>15</v>
-      </c>
       <c r="G4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
+      <c r="A5" s="8"/>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D5">
-        <v>10001</v>
-      </c>
-      <c r="E5" s="12">
+        <v>10002</v>
+      </c>
+      <c r="E5" s="18">
+        <v>1</v>
+      </c>
+      <c r="F5" s="18">
+        <v>2</v>
+      </c>
+      <c r="G5">
         <v>5</v>
-      </c>
-      <c r="F5" s="12">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
+      <c r="A6" s="8"/>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D6">
-        <v>10002</v>
-      </c>
-      <c r="E6">
+        <v>10003</v>
+      </c>
+      <c r="E6" s="18">
+        <v>1</v>
+      </c>
+      <c r="F6" s="18">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <v>5</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
+      <c r="A7" s="8"/>
       <c r="B7">
         <v>4</v>
       </c>
-      <c r="C7" s="2">
-        <v>1003</v>
+      <c r="C7">
+        <v>20001</v>
       </c>
       <c r="D7">
-        <v>10001</v>
-      </c>
-      <c r="E7" s="2">
-        <v>10</v>
-      </c>
-      <c r="F7" s="22">
-        <v>8</v>
+        <v>20001</v>
+      </c>
+      <c r="E7" s="18">
+        <v>5</v>
+      </c>
+      <c r="F7" s="18">
+        <v>1</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -2029,21 +2149,21 @@
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
+      <c r="A8" s="8"/>
       <c r="B8">
         <v>5</v>
       </c>
       <c r="C8" s="2">
-        <v>1003</v>
-      </c>
-      <c r="D8">
-        <v>10002</v>
+        <v>30001</v>
+      </c>
+      <c r="D8" s="2">
+        <v>30001</v>
       </c>
       <c r="E8" s="2">
         <v>10</v>
       </c>
-      <c r="F8" s="22">
-        <v>5</v>
+      <c r="F8" s="18">
+        <v>1</v>
       </c>
       <c r="G8">
         <v>10</v>
@@ -2052,37 +2172,17 @@
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9">
-        <v>6</v>
-      </c>
-      <c r="C9" s="2">
-        <v>1003</v>
-      </c>
-      <c r="D9">
-        <v>10003</v>
-      </c>
-      <c r="E9" s="2">
-        <v>10</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9">
-        <v>10</v>
-      </c>
+      <c r="A9" s="8"/>
+      <c r="F9" s="18"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+      <c r="A10" s="8"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B11"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -2090,70 +2190,526 @@
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="6"/>
-      <c r="C12"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
+      <c r="A13" s="8"/>
       <c r="B13" s="6"/>
-      <c r="C13"/>
-      <c r="D13"/>
+      <c r="E13" s="6"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="C14"/>
-      <c r="D14"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="6"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="D15"/>
+      <c r="A15" s="8"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
+      <c r="A16" s="8"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="D17"/>
+      <c r="A17" s="8"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="D18"/>
+      <c r="A18" s="8"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+      <c r="A19" s="8"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
+      <c r="A20" s="8"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
+      <c r="A21" s="8"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.625" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>30001</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>30001</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>0.7</v>
+      </c>
+      <c r="F5">
+        <v>3002</v>
+      </c>
+      <c r="G5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>30001</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>0.3</v>
+      </c>
+      <c r="F6">
+        <v>3003</v>
+      </c>
+      <c r="G6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>3.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="23" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1001</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1002</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1003</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>2001</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>2001</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>3000</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>3000</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>3000</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>3000</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>3001</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14">
+        <v>3001</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>3002</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>3002</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>3002</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>3003</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>16</v>
+      </c>
+      <c r="C19">
+        <v>3003</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>17</v>
+      </c>
+      <c r="C20">
+        <v>3003</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
 </file>
--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="2"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -851,7 +851,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1979,7 +1979,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="23" customWidth="1"/>
@@ -2130,20 +2130,17 @@
       <c r="B7">
         <v>4</v>
       </c>
-      <c r="C7">
-        <v>20001</v>
+      <c r="C7" s="2">
+        <v>2001</v>
       </c>
       <c r="D7">
-        <v>20001</v>
+        <v>10001</v>
       </c>
       <c r="E7" s="18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F7" s="18">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -2154,63 +2151,149 @@
         <v>5</v>
       </c>
       <c r="C8" s="2">
-        <v>30001</v>
-      </c>
-      <c r="D8" s="2">
-        <v>30001</v>
-      </c>
-      <c r="E8" s="2">
-        <v>10</v>
+        <v>2002</v>
+      </c>
+      <c r="D8">
+        <v>10001</v>
+      </c>
+      <c r="E8" s="18">
+        <v>1</v>
       </c>
       <c r="F8" s="18">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
-      <c r="F9" s="18"/>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2002</v>
+      </c>
+      <c r="D9">
+        <v>10002</v>
+      </c>
+      <c r="E9" s="18">
+        <v>1</v>
+      </c>
+      <c r="F9" s="18">
+        <v>25</v>
+      </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2003</v>
+      </c>
+      <c r="D10">
+        <v>10001</v>
+      </c>
+      <c r="E10" s="18">
+        <v>1</v>
+      </c>
+      <c r="F10" s="18">
+        <v>30</v>
+      </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
+      <c r="A11" s="8"/>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2003</v>
+      </c>
+      <c r="D11">
+        <v>10002</v>
+      </c>
+      <c r="E11" s="18">
+        <v>1</v>
+      </c>
+      <c r="F11" s="18">
+        <v>20</v>
+      </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
+      <c r="A12" s="8"/>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2003</v>
+      </c>
+      <c r="D12">
+        <v>10003</v>
+      </c>
+      <c r="E12" s="18">
+        <v>1</v>
+      </c>
+      <c r="F12" s="18">
+        <v>10</v>
+      </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
-      <c r="B13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>20001</v>
+      </c>
+      <c r="D13">
+        <v>20001</v>
+      </c>
+      <c r="E13" s="18">
+        <v>5</v>
+      </c>
+      <c r="F13" s="18">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
-      <c r="B14" s="6"/>
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2">
+        <v>30001</v>
+      </c>
+      <c r="D14" s="2">
+        <v>30001</v>
+      </c>
+      <c r="E14" s="2">
+        <v>10</v>
+      </c>
+      <c r="F14" s="18">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
+      <c r="F15" s="18"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
@@ -2220,36 +2303,73 @@
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
+      <c r="B19" s="6"/>
+      <c r="E19" s="6"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+      <c r="B20" s="6"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="8"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="8"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="8"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="8"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="8"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>

--- a/Shared/XLS/Monster.xlsx
+++ b/Shared/XLS/Monster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="3"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="633" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -851,7 +851,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1121,7 +1121,7 @@
         <v>14</v>
       </c>
       <c r="J4" s="18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K4" s="18">
         <v>10</v>
@@ -1166,7 +1166,7 @@
         <v>14</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5" s="18">
         <v>10</v>
@@ -1211,7 +1211,7 @@
         <v>14</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K6" s="18">
         <v>10</v>
